--- a/income_details.xlsx
+++ b/income_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -415,35 +415,119 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Salary</v>
+        <v>Freelance</v>
       </c>
       <c r="B2">
-        <v>12300</v>
+        <v>50000</v>
       </c>
       <c r="C2" t="str">
-        <v>2026-02-20</v>
+        <v>2026-02-26</v>
       </c>
       <c r="D2" t="str">
-        <v>💼</v>
+        <v>💻</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="B3">
+        <v>218999</v>
+      </c>
+      <c r="C3" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="D3" t="str">
+        <v>💼</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Freelance</v>
+      </c>
+      <c r="B4">
+        <v>50000</v>
+      </c>
+      <c r="C4" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="D4" t="str">
+        <v>💻</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>Business</v>
       </c>
-      <c r="B3">
+      <c r="B5">
+        <v>10006</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="D5" t="str">
+        <v>🏢</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Investment</v>
+      </c>
+      <c r="B6">
+        <v>50000</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2026-02-26</v>
+      </c>
+      <c r="D6" t="str">
+        <v>📈</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Business</v>
+      </c>
+      <c r="B7">
         <v>400500</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C7" t="str">
         <v>2026-02-17</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D7" t="str">
+        <v>🏢</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>tradings</v>
+      </c>
+      <c r="B8">
+        <v>40000</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="D8" t="str">
+        <v>💰</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Business</v>
+      </c>
+      <c r="B9">
+        <v>6000</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2026-02-08</v>
+      </c>
+      <c r="D9" t="str">
         <v>🏢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>